--- a/inst/templates/PKParameter.xlsx
+++ b/inst/templates/PKParameter.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ztcok\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECAC45F-FA41-46C6-94F2-5C93EE9FA9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="914" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="14" r:id="rId1"/>
-    <sheet name="Userdef PK Parameter" sheetId="15" r:id="rId2"/>
-    <sheet name="Dictionary" sheetId="16" r:id="rId3"/>
+    <sheet name="Template" sheetId="14" state="visible" r:id="rId1"/>
+    <sheet name="Userdef PK Parameter" sheetId="15" state="visible" r:id="rId2"/>
+    <sheet name="_Validity" sheetId="16" state="hidden" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="validity_standardPkParameterValues">'_Validity'!$A$1:$A$22</definedName>
+    <definedName name="validity_pkParameterConcentrationUnitValues">'_Validity'!$A$24:$A$52</definedName>
+    <definedName name="validity_pkParameterTimeUnitValues">'_Validity'!$A$54:$A$61</definedName>
+    <definedName name="validity_pkParameterAucUnitValues">'_Validity'!$A$63:$A$98</definedName>
+    <definedName name="validity_pkParameterFlowPerWeightUnitValues">'_Validity'!$A$100:$A$103</definedName>
+    <definedName name="validity_pkParameterVolumePerBodyWeightUnitValues">'_Validity'!$A$105:$A$107</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t>µg/l</t>
   </si>
@@ -547,13 +548,320 @@
   </si>
   <si>
     <t>used to define dimension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_max_norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_min_norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_trough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_trough_norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC_tEnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC_tEnd_norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUCM_tEnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC_inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC_inf_norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC_tEnd_inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUC_tEnd_inf_norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FractionAucEndToInf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tthreshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µg/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pg/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg/dl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µg/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pg/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmol/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µmol/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nmol/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pmol/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fmol/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmol/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µmol/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nmol/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pmol/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fmol/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">week(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">month(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">year(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µg*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pg*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µg*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pg*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µg*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pg*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µg*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pg*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kg*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmol*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µmol*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nmol*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pmol*h/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmol*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µmol*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nmol*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pmol*h/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmol*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µmol*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nmol*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pmol*min/ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µmol*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmol*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nmol*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pmol*min/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l/min/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l/h/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ml/min/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ml/h/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ml/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µl/kg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,25 +869,21 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <i/>
     </font>
   </fonts>
   <fills count="3">
@@ -608,79 +912,47 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF000080"/>
-      <color rgb="FF800080"/>
-      <color rgb="FF808000"/>
-      <color rgb="FF800000"/>
-      <color rgb="FF808080"/>
-      <color rgb="FF00FFFF"/>
-      <color rgb="FFFF00FF"/>
-      <color rgb="FF008000"/>
-      <color rgb="FF6BD76B"/>
-      <color rgb="FF802268"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -978,18 +1250,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
-    <col min="5" max="5" width="35.625" customWidth="1"/>
+    <col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="27.5" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.25" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="35.625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>41</v>
       </c>
@@ -1006,22 +1278,22 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" ht="51.75" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1031,11 +1303,11 @@
       <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1045,11 +1317,11 @@
       <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,11 +1331,11 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,11 +1345,11 @@
       <c r="C6" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" s="1" t="s">
         <v>81</v>
       </c>
@@ -1087,11 +1359,11 @@
       <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>116</v>
       </c>
@@ -1101,11 +1373,11 @@
       <c r="C8" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1115,11 +1387,11 @@
       <c r="C9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1129,11 +1401,11 @@
       <c r="C10" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1143,11 +1415,11 @@
       <c r="C11" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1157,11 +1429,11 @@
       <c r="C12" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -1171,11 +1443,11 @@
       <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1185,25 +1457,25 @@
       <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>127</v>
       </c>
@@ -1213,11 +1485,11 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>128</v>
       </c>
@@ -1227,11 +1499,11 @@
       <c r="C17" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>129</v>
       </c>
@@ -1241,11 +1513,11 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19" s="1" t="s">
         <v>130</v>
       </c>
@@ -1255,11 +1527,11 @@
       <c r="C19" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>131</v>
       </c>
@@ -1269,11 +1541,11 @@
       <c r="C20" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" s="1" t="s">
         <v>132</v>
       </c>
@@ -1283,11 +1555,11 @@
       <c r="C21" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22" s="1" t="s">
         <v>133</v>
       </c>
@@ -1297,11 +1569,11 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23" s="1" t="s">
         <v>134</v>
       </c>
@@ -1311,11 +1583,11 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24" s="1" t="s">
         <v>135</v>
       </c>
@@ -1325,11 +1597,11 @@
       <c r="C24" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25" s="1" t="s">
         <v>136</v>
       </c>
@@ -1339,11 +1611,11 @@
       <c r="C25" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26" s="1" t="s">
         <v>137</v>
       </c>
@@ -1353,11 +1625,11 @@
       <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27" s="1" t="s">
         <v>138</v>
       </c>
@@ -1367,11 +1639,11 @@
       <c r="C27" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28" s="1" t="s">
         <v>139</v>
       </c>
@@ -1381,11 +1653,11 @@
       <c r="C28" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29" s="1" t="s">
         <v>140</v>
       </c>
@@ -1395,11 +1667,11 @@
       <c r="C29" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -1409,11 +1681,11 @@
       <c r="C30" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -1423,25 +1695,25 @@
       <c r="C31" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
@@ -1451,11 +1723,11 @@
       <c r="C33" t="s">
         <v>1</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34" s="1" t="s">
         <v>20</v>
       </c>
@@ -1465,43 +1737,59 @@
       <c r="C34" t="s">
         <v>1</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>167</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid value. Please select from the list" xr:uid="{00000000-0002-0000-0600-000000000000}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Dictionary!$A$2:$A$29</xm:f>
+            <xm:f>validity_pkParameterConcentrationUnitValues</xm:f>
           </x14:formula1>
           <xm:sqref>C3:C4 C6 C16:C19 C22:C23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid value. Please select from the list" xr:uid="{00000000-0002-0000-0600-000001000000}">
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Dictionary!$B$2:$B$9</xm:f>
+            <xm:f>validity_pkParameterTimeUnitValues</xm:f>
           </x14:formula1>
           <xm:sqref>C32 C5 C11:C12 C20:C21</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid value. Please select from the list" xr:uid="{00000000-0002-0000-0600-000002000000}">
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Dictionary!$C$2:$C$37</xm:f>
+            <xm:f>validity_pkParameterAucUnitValues</xm:f>
           </x14:formula1>
           <xm:sqref>C7:C10 C24:C31</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid value. Please select from the list" xr:uid="{00000000-0002-0000-0600-000003000000}">
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Dictionary!$D$2:$D$5</xm:f>
+            <xm:f>validity_pkParameterFlowPerWeightUnitValues</xm:f>
           </x14:formula1>
           <xm:sqref>C13</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid value. Please select from the list" xr:uid="{00000000-0002-0000-0600-000004000000}">
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Dictionary!$E$2:$E$3</xm:f>
+            <xm:f>validity_pkParameterVolumePerBodyWeightUnitValues</xm:f>
           </x14:formula1>
           <xm:sqref>C14:C15</xm:sqref>
         </x14:dataValidation>
@@ -1512,23 +1800,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="1"/>
-    <col min="2" max="2" width="27.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="8" max="8" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.875" customWidth="1"/>
+    <col min="1" max="1" width="12.625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="27.625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="9.375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="19.75" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.75" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.125" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="14.5" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="18.5" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="22.875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>41</v>
       </c>
@@ -1565,26 +1853,26 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" s="10" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" ht="25.5" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1595,7 +1883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1616,15 +1904,15 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid value. Please select from the list" xr:uid="{00000000-0002-0000-0500-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Dictionary!$F$2:$F$22</xm:f>
+            <xm:f>validity_standardPkParameterValues</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:B101</xm:sqref>
+          <xm:sqref>B2:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1633,409 +1921,525 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1">
+      <c r="A1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="F22" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C35" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C36" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C37" t="s">
-        <v>115</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>